--- a/ВПКС.xlsx
+++ b/ВПКС.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaces\Desktop\programm\course_forth\VPKS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF43A082-EDA3-4356-A992-2DCD01DC0F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BC4AFB-0F9E-46DD-B386-A5188D820BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3765" windowWidth="18750" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="3300" windowWidth="18750" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лабораторные" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="12">
   <si>
     <t>№</t>
   </si>
@@ -180,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -219,11 +219,35 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -529,41 +553,43 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="5.7109375" customWidth="1"/>
-    <col min="7" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="12" max="12" width="4.5703125" customWidth="1"/>
+    <col min="2" max="8" width="5.7109375" customWidth="1"/>
+    <col min="9" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+    <col min="14" max="14" width="4.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="7" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -582,64 +608,72 @@
       <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="9">
-        <f t="shared" ref="G2:G12" si="0">COUNTIF(B2:F2,"!") + COUNTIF(B2:F2,"+")</f>
-        <v>5</v>
-      </c>
-      <c r="H2" s="10">
-        <f t="shared" ref="H2:H13" si="1">COUNTIF(B2:F2,"+")</f>
-        <v>5</v>
-      </c>
-      <c r="I2" s="10">
-        <v>5</v>
-      </c>
-      <c r="J2" s="8"/>
-      <c r="L2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="9">
+        <f>COUNTIF(B2:F2,"!") + COUNTIF(B2:F2,"+")</f>
+        <v>5</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(B2:F2,"+")</f>
+        <v>5</v>
+      </c>
+      <c r="K2" s="10">
+        <v>5</v>
+      </c>
+      <c r="L2" s="8"/>
+      <c r="N2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
         <v>7</v>
       </c>
-      <c r="J3" s="8"/>
-      <c r="L3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="1" t="s">
+      <c r="G3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="11">
+        <f>COUNTIF(B3:H3,"!") + COUNTIF(B3:H3,"+")</f>
+        <v>7</v>
+      </c>
+      <c r="J3" s="5">
+        <f>COUNTIF(B3:F3,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>7</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="N3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -658,26 +692,28 @@
       <c r="F4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="H4" s="10">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="I4" s="10">
-        <v>5</v>
-      </c>
-      <c r="J4" s="8"/>
-      <c r="L4" s="4" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="9">
+        <f>COUNTIF(B4:F4,"!") + COUNTIF(B4:F4,"+")</f>
+        <v>5</v>
+      </c>
+      <c r="J4" s="10">
+        <f>COUNTIF(B4:F4,"+")</f>
+        <v>5</v>
+      </c>
+      <c r="K4" s="10">
+        <v>5</v>
+      </c>
+      <c r="L4" s="8"/>
+      <c r="N4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -696,20 +732,26 @@
       <c r="F5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="11">
+        <f>COUNTIF(B5:F5,"!") + COUNTIF(B5:F5,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <f>COUNTIF(B5:F5,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -728,20 +770,26 @@
       <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="11">
+        <f>COUNTIF(B6:F6,"!") + COUNTIF(B6:F6,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <f>COUNTIF(B6:F6,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -760,20 +808,26 @@
       <c r="F7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="11">
+        <f>COUNTIF(B7:F7,"!") + COUNTIF(B7:F7,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <f>COUNTIF(B7:F7,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -792,20 +846,26 @@
       <c r="F8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="11">
+        <f>COUNTIF(B8:F8,"!") + COUNTIF(B8:F8,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <f>COUNTIF(B8:F8,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -824,20 +884,26 @@
       <c r="F9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="11">
+        <f>COUNTIF(B9:F9,"!") + COUNTIF(B9:F9,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <f>COUNTIF(B9:F9,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -856,20 +922,26 @@
       <c r="F10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="11">
+        <f>COUNTIF(B10:F10,"!") + COUNTIF(B10:F10,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <f>COUNTIF(B10:F10,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -888,20 +960,26 @@
       <c r="F11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="11">
+        <f>COUNTIF(B11:F11,"!") + COUNTIF(B11:F11,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <f>COUNTIF(B11:F11,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -920,20 +998,26 @@
       <c r="F12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
-        <v>0</v>
-      </c>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="11">
+        <f>COUNTIF(B12:F12,"!") + COUNTIF(B12:F12,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <f>COUNTIF(B12:F12,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -952,31 +1036,37 @@
       <c r="F13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="11">
-        <f t="shared" ref="G8:G13" si="2">COUNTIF(B13:F13,"!") + COUNTIF(B13:F13,"+")</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8"/>
+      <c r="G13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="11">
+        <f t="shared" ref="I13" si="0">COUNTIF(B13:F13,"!") + COUNTIF(B13:F13,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <f>COUNTIF(B13:F13,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B2:F13">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+  <conditionalFormatting sqref="B2:H13">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"!"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"+"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ВПКС.xlsx
+++ b/ВПКС.xlsx
@@ -115,7 +115,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -151,11 +151,37 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -185,16 +211,25 @@
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="8" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -719,7 +754,7 @@
     <col customWidth="1" min="2" max="6" width="5.7109375"/>
     <col customWidth="1" min="7" max="9" width="10.7109375"/>
     <col customWidth="1" min="10" max="10" width="23"/>
-    <col customWidth="1" min="12" max="12" width="4.5703125"/>
+    <col customWidth="1" min="12" max="12" width="2.8515625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -788,22 +823,22 @@
       <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="12">
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="11">
         <v>7</v>
       </c>
       <c r="H3" s="6">
@@ -813,7 +848,7 @@
         <v>7</v>
       </c>
       <c r="J3" s="7"/>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>8</v>
       </c>
       <c r="M3" s="9" t="s">
@@ -851,7 +886,7 @@
         <v>5</v>
       </c>
       <c r="J4" s="7"/>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="13" t="s">
         <v>10</v>
       </c>
       <c r="M4" s="9" t="s">
@@ -862,31 +897,29 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="15">
+      <c r="B5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
+        <v>4</v>
+      </c>
+      <c r="H5" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I5" s="6">
+        <v>4</v>
       </c>
       <c r="J5" s="7"/>
     </row>
@@ -894,31 +927,29 @@
       <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="15">
+      <c r="B6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="17"/>
+      <c r="G6" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
+        <v>4</v>
+      </c>
+      <c r="H6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I6" s="6">
+        <v>4</v>
       </c>
       <c r="J6" s="7"/>
     </row>
@@ -941,7 +972,7 @@
       <c r="F7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -950,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J7" s="7"/>
     </row>
@@ -973,7 +1004,7 @@
       <c r="F8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -982,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J8" s="7"/>
     </row>
@@ -1005,7 +1036,7 @@
       <c r="F9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1014,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J9" s="7"/>
     </row>
@@ -1037,7 +1068,7 @@
       <c r="F10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="18">
         <f t="shared" ref="G10:G13" si="2">COUNTIF(B10:F10,"!") + COUNTIF(B10:F10,"+")</f>
         <v>0</v>
       </c>
@@ -1046,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" s="7"/>
     </row>
@@ -1069,7 +1100,7 @@
       <c r="F11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1078,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J11" s="7"/>
     </row>
@@ -1101,7 +1132,7 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1110,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" s="7"/>
     </row>
@@ -1133,7 +1164,7 @@
       <c r="F13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1142,13 +1173,143 @@
         <v>0</v>
       </c>
       <c r="I13" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13" s="7"/>
     </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="10">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="18">
+        <f>COUNTIF(B14:F14,"!")+COUNTIF(B14:F14,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <f>COUNTIF(B14:F14,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>5</v>
+      </c>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="10">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="18">
+        <f>COUNTIF(B15:F15,"!")+COUNTIF(B15:F15,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <f>COUNTIF(B15:F15,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>5</v>
+      </c>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="10">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="18">
+        <f>COUNTIF(B16:F16,"!")+COUNTIF(B16:F16,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <f>COUNTIF(B16:F16,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>5</v>
+      </c>
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="18">
+        <f>COUNTIF(B17:F17,"!")+COUNTIF(B17:F17,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <f>COUNTIF(B17:F17,"+")</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>5</v>
+      </c>
+      <c r="J17" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1158,7 +1319,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{001600B6-00B7-4C18-AF8C-00EE000C00EF}">
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{00B800F0-002B-4CCD-B56B-00EA006900F3}">
             <xm:f>"+"</xm:f>
             <x14:dxf>
               <fill>
@@ -1169,10 +1330,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B2:F2 B3 B4:F13 C3 D3 E3 F3 G3 H3</xm:sqref>
+          <xm:sqref>B2:F2 B3 B4:F13 C3 D3 E3 F3 G3 H3 B14:F14 B15:F15 B16:F16 B17:F17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{00EB005C-0006-4FA6-8288-000C003F0010}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{000D00A7-0099-4E61-A9ED-007400450009}">
             <xm:f>"-"</xm:f>
             <x14:dxf>
               <fill>
@@ -1183,10 +1344,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B2:F2 B3 B4:F13 C3 D3 E3 F3 G3 H3</xm:sqref>
+          <xm:sqref>B2:F2 B3 B4:F13 C3 D3 E3 F3 G3 H3 B14:F14 B15:F15 B16:F16 B17:F17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{00400018-00AA-40A4-8F30-00C7003000BE}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{00B200F5-00B6-47E2-A1A3-008A006A0019}">
             <xm:f>"!"</xm:f>
             <x14:dxf>
               <fill>
@@ -1197,7 +1358,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B2:F2 B3 B4:F13 C3 D3 E3 F3 G3 H3</xm:sqref>
+          <xm:sqref>B2:F2 B3 B4:F13 C3 D3 E3 F3 G3 H3 B14:F14 B15:F15 B16:F16 B17:F17</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
